--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62370.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62370.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>IG.1103</t>
+          <t>16.1103</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1831-91-01</t>
+          <t>S1-01-G1</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hiain l nf</t>
+          <t>Hd</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GCQC</t>
+          <t>KG</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G59G</t>
+          <t>G59B</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>69876</v>
+        <v>68370</v>
       </c>
     </row>
     <row r="18">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62370.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62370.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G59B</t>
+          <t>G82G</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62370.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62370.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hd</t>
+          <t>Ma</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>RG</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         <v>0.26</v>
       </c>
       <c r="K4" t="n">
-        <v>10011</v>
+        <v>10041</v>
       </c>
     </row>
     <row r="5">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62370.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62370.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>MA</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62370.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62370.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -706,7 +706,7 @@
         <v>0.26</v>
       </c>
       <c r="K4" t="n">
-        <v>10041</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
